--- a/WWHALigaData.xlsx
+++ b/WWHALigaData.xlsx
@@ -415,9 +415,912 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Manager Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Team Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gameweek</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Player Out</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Out - Team</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Out - Position</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Player In</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>In - Team</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>In - Position</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Free Hit Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex Stephenson</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ajax Hamsterdam</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Palestra</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>De Cuyper</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ben Davies</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The Goodison Gang</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Shaw</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Konsa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chuka Iwobi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Only Wan Iwobi</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sarr</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chuka Iwobi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Only Wan Iwobi</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cunha</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>M.Sangaré</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ieuan Davies</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Expected Letdowns</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cunha</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jen Barton</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hardly Athletic</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>E.Le Fée</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>M.Sangaré</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pedro Porro</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Spurs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>De Cuyper</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gibbs-White</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nott'm Forest</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Calafiori</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mendy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sarr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>M.Sangaré</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Watkins</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Matt Hall</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Jacquet Spuds</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Spence</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Spurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>De Cuyper</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Richard Hamlett</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>kiliHAM-jaros</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Verbruggen</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Goalkeeper</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dubravka</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Spurs</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Goalkeeper</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rob Grainger</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ragey City</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Watkins</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Wissa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sam Jones</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mainoo Knighted</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Calafiori</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Seema Thomas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Haa Haa Haalanderers</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Thiago</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Barry</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The Gareth</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dunning Krugger FC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Gibbs-White</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nott'm Forest</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tavernier</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -506,12 +1409,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rob Grainger</t>
+          <t>Craig Davis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ragey City</t>
+          <t>Memyselfandi1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -534,10 +1437,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -578,12 +1479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Luke Morris</t>
+          <t>Richard Hamlett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Isak at this game</t>
+          <t>kiliHAM-jaros</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -648,12 +1549,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jamie jones</t>
+          <t>Luke Morris</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Game of Jones</t>
+          <t>Isak at this game</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -718,12 +1619,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Connor Keys</t>
+          <t>Isaac Parr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Xabi Dabi Doo</t>
+          <t>Los Porros Hermanos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -790,12 +1691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Davies</t>
+          <t>Connor Keys</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Goodison Gang</t>
+          <t>Xabi Dabi Doo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -862,12 +1763,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gareth Davis</t>
+          <t>Alex Stephenson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Iraola Coaster</t>
+          <t>Ajax Hamsterdam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -890,8 +1791,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -932,12 +1835,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sam Jones</t>
+          <t>Sam Green</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mainoo Knighted</t>
+          <t>Yoro Wizard Harry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1004,12 +1907,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Hamlett</t>
+          <t>Robin Jones</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kiliHAM-jaros</t>
+          <t>The Last Dance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1032,8 +1935,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1074,12 +1979,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Craig Davis</t>
+          <t>Gary Snoad-Jones</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Memyselfandi1</t>
+          <t>The Pursuit of Craig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1146,12 +2051,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Isaac Parr</t>
+          <t>Rob Grainger</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Los Porros Hermanos</t>
+          <t>Ragey City</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1218,12 +2123,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alex Stephenson</t>
+          <t>Craig Jones</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajax Hamsterdam</t>
+          <t>One Andoni Bosh FC !</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1246,10 +2151,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1290,12 +2193,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fantasy Elliot</t>
+          <t>jamie jones</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xabi Road</t>
+          <t>Game of Jones</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1318,10 +2221,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1362,12 +2263,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Craig Jones</t>
+          <t>Sam Jones</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>One Andoni Bosh FC !</t>
+          <t>Mainoo Knighted</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1434,12 +2335,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kieran O'Brien</t>
+          <t>rodwyn hughes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lana Del Gavin Rae</t>
+          <t>Parkyking</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1506,12 +2407,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Robin Jones</t>
+          <t>Gareth Davis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Last Dance</t>
+          <t>Iraola Coaster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1534,10 +2435,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" t="n">
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1578,12 +2477,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gary Snoad-Jones</t>
+          <t>Dan Huskings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Pursuit of Craig</t>
+          <t>Dantastic Blue Army</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1650,12 +2549,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sam Green</t>
+          <t>Fantasy Elliot</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yoro Wizard Harry</t>
+          <t>Xabi Road</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1722,12 +2621,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jen Barton</t>
+          <t>Ben Davies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hardly Athletic</t>
+          <t>The Goodison Gang</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1794,12 +2693,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ciaran Lewis</t>
+          <t>Ieuan Davies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ciaran's Team</t>
+          <t>Expected Letdowns</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1866,12 +2765,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ieuan Davies</t>
+          <t>Chuka Iwobi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expected Letdowns</t>
+          <t>Only Wan Iwobi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1894,10 +2793,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" t="n">
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1938,12 +2835,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rodwyn hughes</t>
+          <t>Kieran O'Brien</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parkyking</t>
+          <t>Lana Del Gavin Rae</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2010,12 +2907,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Leah Jenkins</t>
+          <t>Jen Barton</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GoEzEoNmE</t>
+          <t>Hardly Athletic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2082,12 +2979,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Seema Thomas</t>
+          <t>Simon Pickthall</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Haa Haa Haalanderers</t>
+          <t>Dejan Kuluspursy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2154,12 +3051,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dan Huskings</t>
+          <t>Seema Thomas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dantastic Blue Army</t>
+          <t>Haa Haa Haalanderers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2226,12 +3123,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matt Hall</t>
+          <t>Ciaran Lewis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Jacquet Spuds</t>
+          <t>Ciaran's Team</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2298,12 +3195,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Simon Pickthall</t>
+          <t>The Gareth</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dejan Kuluspursy</t>
+          <t>Dunning Krugger FC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2370,12 +3267,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Gareth</t>
+          <t>Matt Hall</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dunning Krugger FC</t>
+          <t>The Jacquet Spuds</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2442,12 +3339,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chuka Iwobi</t>
+          <t>Mike Sanders</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Only Wan Iwobi</t>
+          <t>Spursie</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2514,12 +3411,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mike Sanders</t>
+          <t>Leah Jenkins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spursie</t>
+          <t>GoEzEoNmE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2594,7 +3491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,12 +3534,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rob Grainger</t>
+          <t>Craig Davis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ragey City</t>
+          <t>Memyselfandi1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2650,11 +3547,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saka</t>
+          <t>João Pedro</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2670,12 +3567,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Luke Morris</t>
+          <t>Richard Hamlett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Isak at this game</t>
+          <t>kiliHAM-jaros</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2683,7 +3580,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2703,12 +3600,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jamie jones</t>
+          <t>Luke Morris</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Game of Jones</t>
+          <t>Isak at this game</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2736,12 +3633,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Connor Keys</t>
+          <t>Isaac Parr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Xabi Dabi Doo</t>
+          <t>Los Porros Hermanos</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2749,7 +3646,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2769,12 +3666,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Davies</t>
+          <t>Connor Keys</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Goodison Gang</t>
+          <t>Xabi Dabi Doo</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2782,7 +3679,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2802,12 +3699,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gareth Davis</t>
+          <t>Alex Stephenson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Iraola Coaster</t>
+          <t>Ajax Hamsterdam</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2815,7 +3712,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2835,12 +3732,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sam Jones</t>
+          <t>Sam Green</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mainoo Knighted</t>
+          <t>Yoro Wizard Harry</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2848,7 +3745,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mbeumo</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2868,12 +3765,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Hamlett</t>
+          <t>Robin Jones</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kiliHAM-jaros</t>
+          <t>The Last Dance</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2901,12 +3798,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Craig Davis</t>
+          <t>Gary Snoad-Jones</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Memyselfandi1</t>
+          <t>The Pursuit of Craig</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2914,11 +3811,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>João Pedro</t>
+          <t>Havertz</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2934,12 +3831,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Isaac Parr</t>
+          <t>Rob Grainger</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Los Porros Hermanos</t>
+          <t>Ragey City</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2947,11 +3844,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>Saka</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2967,12 +3864,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alex Stephenson</t>
+          <t>Craig Jones</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajax Hamsterdam</t>
+          <t>One Andoni Bosh FC !</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2980,7 +3877,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3000,12 +3897,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fantasy Elliot</t>
+          <t>jamie jones</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xabi Road</t>
+          <t>Game of Jones</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3033,12 +3930,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Craig Jones</t>
+          <t>Sam Jones</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>One Andoni Bosh FC !</t>
+          <t>Mainoo Knighted</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3046,7 +3943,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>Mbeumo</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -3066,12 +3963,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kieran O'Brien</t>
+          <t>rodwyn hughes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lana Del Gavin Rae</t>
+          <t>Parkyking</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3079,7 +3976,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -3099,12 +3996,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Robin Jones</t>
+          <t>Gareth Davis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Last Dance</t>
+          <t>Iraola Coaster</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3112,7 +4009,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -3132,12 +4029,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gary Snoad-Jones</t>
+          <t>Dan Huskings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Pursuit of Craig</t>
+          <t>Dantastic Blue Army</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3145,11 +4042,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Havertz</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3165,12 +4062,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sam Green</t>
+          <t>Fantasy Elliot</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yoro Wizard Harry</t>
+          <t>Xabi Road</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3198,12 +4095,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jen Barton</t>
+          <t>Ben Davies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hardly Athletic</t>
+          <t>The Goodison Gang</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3231,12 +4128,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ciaran Lewis</t>
+          <t>Ieuan Davies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ciaran's Team</t>
+          <t>Expected Letdowns</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3244,11 +4141,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>Havertz</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3264,12 +4161,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ieuan Davies</t>
+          <t>Chuka Iwobi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expected Letdowns</t>
+          <t>Only Wan Iwobi</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3277,11 +4174,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Havertz</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3297,12 +4194,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rodwyn hughes</t>
+          <t>Kieran O'Brien</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parkyking</t>
+          <t>Lana Del Gavin Rae</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3310,7 +4207,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3330,12 +4227,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Leah Jenkins</t>
+          <t>Jen Barton</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GoEzEoNmE</t>
+          <t>Hardly Athletic</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3343,11 +4240,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Calvert-Lewin</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3363,12 +4260,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Seema Thomas</t>
+          <t>Simon Pickthall</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Haa Haa Haalanderers</t>
+          <t>Dejan Kuluspursy</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3376,7 +4273,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Haaland</t>
+          <t>B.Fernandes</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3396,12 +4293,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dan Huskings</t>
+          <t>Seema Thomas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dantastic Blue Army</t>
+          <t>Haa Haa Haalanderers</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3429,12 +4326,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matt Hall</t>
+          <t>Ciaran Lewis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Jacquet Spuds</t>
+          <t>Ciaran's Team</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3442,7 +4339,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Isak</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3462,12 +4359,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Simon Pickthall</t>
+          <t>The Gareth</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dejan Kuluspursy</t>
+          <t>Dunning Krugger FC</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3475,11 +4372,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3495,12 +4392,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Gareth</t>
+          <t>Matt Hall</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dunning Krugger FC</t>
+          <t>The Jacquet Spuds</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3508,11 +4405,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Isak</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3528,12 +4425,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chuka Iwobi</t>
+          <t>Mike Sanders</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Only Wan Iwobi</t>
+          <t>Spursie</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3541,7 +4438,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B.Fernandes</t>
+          <t>Haaland</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3561,12 +4458,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mike Sanders</t>
+          <t>Leah Jenkins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spursie</t>
+          <t>GoEzEoNmE</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3574,18 +4471,975 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Craig Davis</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Memyselfandi1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Richard Hamlett</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>kiliHAM-jaros</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>23</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Luke Morris</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Isak at this game</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Haaland</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="E33" t="n">
+        <v>13</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Isaac Parr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Los Porros Hermanos</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>23</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Connor Keys</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Xabi Dabi Doo</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Alex Stephenson</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ajax Hamsterdam</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sam Green</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Yoro Wizard Harry</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>13</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Robin Jones</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Last Dance</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>23</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gary Snoad-Jones</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The Pursuit of Craig</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>23</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Rob Grainger</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ragey City</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Craig Jones</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>One Andoni Bosh FC !</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>13</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>jamie jones</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Game of Jones</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sam Jones</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mainoo Knighted</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>rodwyn hughes</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Parkyking</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gareth Davis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Iraola Coaster</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Szoboszlai</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dan Huskings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Dantastic Blue Army</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>13</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Fantasy Elliot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Xabi Road</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>13</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ben Davies</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>The Goodison Gang</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ieuan Davies</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Expected Letdowns</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>23</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chuka Iwobi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Only Wan Iwobi</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kieran O'Brien</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Lana Del Gavin Rae</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>13</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jen Barton</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hardly Athletic</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Tzolis</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Simon Pickthall</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dejan Kuluspursy</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>B.Fernandes</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>23</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Seema Thomas</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Haa Haa Haalanderers</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciaran Lewis</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ciaran's Team</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>The Gareth</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Dunning Krugger FC</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Saka</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Matt Hall</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The Jacquet Spuds</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Isak</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mike Sanders</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Spursie</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Haaland</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Leah Jenkins</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GoEzEoNmE</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>João Pedro</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
